--- a/artfynd/A 34086-2023 artfynd.xlsx
+++ b/artfynd/A 34086-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY71"/>
+  <dimension ref="A1:AY74"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -8662,6 +8662,341 @@
       </c>
       <c r="AY71" t="inlineStr"/>
     </row>
+    <row r="72">
+      <c r="A72" t="n">
+        <v>103249684</v>
+      </c>
+      <c r="B72" t="n">
+        <v>99761</v>
+      </c>
+      <c r="C72" t="inlineStr">
+        <is>
+          <t>Godkänd baserat på observatörens uppgifter</t>
+        </is>
+      </c>
+      <c r="D72" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E72" t="n">
+        <v>1365</v>
+      </c>
+      <c r="F72" t="inlineStr">
+        <is>
+          <t>Lappranunkel</t>
+        </is>
+      </c>
+      <c r="G72" t="inlineStr">
+        <is>
+          <t>Coptidium lapponicum</t>
+        </is>
+      </c>
+      <c r="H72" t="inlineStr">
+        <is>
+          <t>(L.) Tzvelev</t>
+        </is>
+      </c>
+      <c r="I72" t="inlineStr"/>
+      <c r="P72" t="inlineStr">
+        <is>
+          <t>Baksjöån, Ås lm</t>
+        </is>
+      </c>
+      <c r="Q72" t="n">
+        <v>609229</v>
+      </c>
+      <c r="R72" t="n">
+        <v>7179129</v>
+      </c>
+      <c r="S72" t="n">
+        <v>25</v>
+      </c>
+      <c r="T72" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U72" t="inlineStr">
+        <is>
+          <t>Vilhelmina</t>
+        </is>
+      </c>
+      <c r="V72" t="inlineStr">
+        <is>
+          <t>Åsele lappmark</t>
+        </is>
+      </c>
+      <c r="W72" t="inlineStr">
+        <is>
+          <t>Vilhelmina</t>
+        </is>
+      </c>
+      <c r="Y72" t="inlineStr">
+        <is>
+          <t>2022-08-22</t>
+        </is>
+      </c>
+      <c r="Z72" t="inlineStr">
+        <is>
+          <t>11:16</t>
+        </is>
+      </c>
+      <c r="AA72" t="inlineStr">
+        <is>
+          <t>2022-08-22</t>
+        </is>
+      </c>
+      <c r="AB72" t="inlineStr">
+        <is>
+          <t>11:16</t>
+        </is>
+      </c>
+      <c r="AD72" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE72" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG72" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT72" t="inlineStr"/>
+      <c r="AW72" t="inlineStr">
+        <is>
+          <t>Isak Vahlström</t>
+        </is>
+      </c>
+      <c r="AX72" t="inlineStr">
+        <is>
+          <t>Isak Vahlström</t>
+        </is>
+      </c>
+      <c r="AY72" t="inlineStr"/>
+    </row>
+    <row r="73">
+      <c r="A73" t="n">
+        <v>114726826</v>
+      </c>
+      <c r="B73" t="n">
+        <v>99761</v>
+      </c>
+      <c r="C73" t="inlineStr">
+        <is>
+          <t>Godkänd baserat på observatörens uppgifter</t>
+        </is>
+      </c>
+      <c r="D73" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E73" t="n">
+        <v>1365</v>
+      </c>
+      <c r="F73" t="inlineStr">
+        <is>
+          <t>Lappranunkel</t>
+        </is>
+      </c>
+      <c r="G73" t="inlineStr">
+        <is>
+          <t>Coptidium lapponicum</t>
+        </is>
+      </c>
+      <c r="H73" t="inlineStr">
+        <is>
+          <t>(L.) Tzvelev</t>
+        </is>
+      </c>
+      <c r="I73" t="inlineStr"/>
+      <c r="P73" t="inlineStr">
+        <is>
+          <t>Baksjöån, Ås lm</t>
+        </is>
+      </c>
+      <c r="Q73" t="n">
+        <v>609404</v>
+      </c>
+      <c r="R73" t="n">
+        <v>7179337</v>
+      </c>
+      <c r="S73" t="n">
+        <v>25</v>
+      </c>
+      <c r="T73" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U73" t="inlineStr">
+        <is>
+          <t>Vilhelmina</t>
+        </is>
+      </c>
+      <c r="V73" t="inlineStr">
+        <is>
+          <t>Åsele lappmark</t>
+        </is>
+      </c>
+      <c r="W73" t="inlineStr">
+        <is>
+          <t>Vilhelmina</t>
+        </is>
+      </c>
+      <c r="X73" t="inlineStr">
+        <is>
+          <t>AC-Vil-0132</t>
+        </is>
+      </c>
+      <c r="Y73" t="inlineStr">
+        <is>
+          <t>2022-08-22</t>
+        </is>
+      </c>
+      <c r="AA73" t="inlineStr">
+        <is>
+          <t>2022-08-22</t>
+        </is>
+      </c>
+      <c r="AD73" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE73" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG73" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT73" t="inlineStr"/>
+      <c r="AW73" t="inlineStr">
+        <is>
+          <t>Sofia Lund</t>
+        </is>
+      </c>
+      <c r="AX73" t="inlineStr">
+        <is>
+          <t>Isak Vahlström</t>
+        </is>
+      </c>
+      <c r="AY73" t="inlineStr">
+        <is>
+          <t>Floraväkteri Sverige</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="n">
+        <v>103249685</v>
+      </c>
+      <c r="B74" t="n">
+        <v>99761</v>
+      </c>
+      <c r="C74" t="inlineStr">
+        <is>
+          <t>Godkänd baserat på observatörens uppgifter</t>
+        </is>
+      </c>
+      <c r="D74" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E74" t="n">
+        <v>1365</v>
+      </c>
+      <c r="F74" t="inlineStr">
+        <is>
+          <t>Lappranunkel</t>
+        </is>
+      </c>
+      <c r="G74" t="inlineStr">
+        <is>
+          <t>Coptidium lapponicum</t>
+        </is>
+      </c>
+      <c r="H74" t="inlineStr">
+        <is>
+          <t>(L.) Tzvelev</t>
+        </is>
+      </c>
+      <c r="I74" t="inlineStr"/>
+      <c r="P74" t="inlineStr">
+        <is>
+          <t>Baksjöån, Ås lm</t>
+        </is>
+      </c>
+      <c r="Q74" t="n">
+        <v>609235</v>
+      </c>
+      <c r="R74" t="n">
+        <v>7179122</v>
+      </c>
+      <c r="S74" t="n">
+        <v>25</v>
+      </c>
+      <c r="T74" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U74" t="inlineStr">
+        <is>
+          <t>Vilhelmina</t>
+        </is>
+      </c>
+      <c r="V74" t="inlineStr">
+        <is>
+          <t>Åsele lappmark</t>
+        </is>
+      </c>
+      <c r="W74" t="inlineStr">
+        <is>
+          <t>Vilhelmina</t>
+        </is>
+      </c>
+      <c r="Y74" t="inlineStr">
+        <is>
+          <t>2022-08-22</t>
+        </is>
+      </c>
+      <c r="Z74" t="inlineStr">
+        <is>
+          <t>11:16</t>
+        </is>
+      </c>
+      <c r="AA74" t="inlineStr">
+        <is>
+          <t>2022-08-22</t>
+        </is>
+      </c>
+      <c r="AB74" t="inlineStr">
+        <is>
+          <t>11:16</t>
+        </is>
+      </c>
+      <c r="AD74" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE74" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG74" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT74" t="inlineStr"/>
+      <c r="AW74" t="inlineStr">
+        <is>
+          <t>Isak Vahlström</t>
+        </is>
+      </c>
+      <c r="AX74" t="inlineStr">
+        <is>
+          <t>Isak Vahlström</t>
+        </is>
+      </c>
+      <c r="AY74" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 34086-2023 artfynd.xlsx
+++ b/artfynd/A 34086-2023 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 34086-2023 artfynd.xlsx
+++ b/artfynd/A 34086-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY71"/>
+  <dimension ref="A1:AY69"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -6802,10 +6802,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>103249641</v>
+        <v>103249650</v>
       </c>
       <c r="B56" t="n">
-        <v>78503</v>
+        <v>76863</v>
       </c>
       <c r="C56" t="inlineStr">
         <is>
@@ -6814,25 +6814,25 @@
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>6456</v>
+        <v>498</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Liten sotlav</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Acolium karelicum</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(Vain.) M.Prieto &amp; Wedin</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
@@ -6842,10 +6842,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>609254.3749908411</v>
+        <v>609173.9886589505</v>
       </c>
       <c r="R56" t="n">
-        <v>7179566.082353068</v>
+        <v>7179514.828837393</v>
       </c>
       <c r="S56" t="n">
         <v>25</v>
@@ -6877,7 +6877,7 @@
       </c>
       <c r="Z56" t="inlineStr">
         <is>
-          <t>13:35</t>
+          <t>13:24</t>
         </is>
       </c>
       <c r="AA56" t="inlineStr">
@@ -6887,7 +6887,7 @@
       </c>
       <c r="AB56" t="inlineStr">
         <is>
-          <t>13:35</t>
+          <t>13:24</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -6914,10 +6914,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>103249650</v>
+        <v>103249653</v>
       </c>
       <c r="B57" t="n">
-        <v>76863</v>
+        <v>89410</v>
       </c>
       <c r="C57" t="inlineStr">
         <is>
@@ -6926,25 +6926,25 @@
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>498</v>
+        <v>5432</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Liten sotlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Acolium karelicum</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Vain.) M.Prieto &amp; Wedin</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
@@ -6954,10 +6954,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>609173.9886589505</v>
+        <v>609179.482900855</v>
       </c>
       <c r="R57" t="n">
-        <v>7179514.828837393</v>
+        <v>7179493.208754918</v>
       </c>
       <c r="S57" t="n">
         <v>25</v>
@@ -6989,7 +6989,7 @@
       </c>
       <c r="Z57" t="inlineStr">
         <is>
-          <t>13:24</t>
+          <t>13:22</t>
         </is>
       </c>
       <c r="AA57" t="inlineStr">
@@ -6999,7 +6999,7 @@
       </c>
       <c r="AB57" t="inlineStr">
         <is>
-          <t>13:24</t>
+          <t>13:22</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -7026,37 +7026,37 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>103249653</v>
+        <v>103249622</v>
       </c>
       <c r="B58" t="n">
-        <v>89410</v>
+        <v>99882</v>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Ovaliderad</t>
+          <t>Godkänd baserat på observatörens uppgifter</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>5432</v>
+        <v>1365</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Lappranunkel</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Coptidium lapponicum</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Tzvelev</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
@@ -7066,10 +7066,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>609179.482900855</v>
+        <v>609404</v>
       </c>
       <c r="R58" t="n">
-        <v>7179493.208754918</v>
+        <v>7179337</v>
       </c>
       <c r="S58" t="n">
         <v>25</v>
@@ -7101,7 +7101,7 @@
       </c>
       <c r="Z58" t="inlineStr">
         <is>
-          <t>13:22</t>
+          <t>14:12</t>
         </is>
       </c>
       <c r="AA58" t="inlineStr">
@@ -7111,7 +7111,7 @@
       </c>
       <c r="AB58" t="inlineStr">
         <is>
-          <t>13:22</t>
+          <t>14:12</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -7138,37 +7138,37 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>103249622</v>
+        <v>103249634</v>
       </c>
       <c r="B59" t="n">
-        <v>99882</v>
+        <v>73686</v>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Godkänd baserat på observatörens uppgifter</t>
+          <t>Ovaliderad</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E59" t="n">
-        <v>1365</v>
+        <v>308</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Lappranunkel</t>
+          <t>Brunpudrad nållav</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Coptidium lapponicum</t>
+          <t>Chaenotheca gracillima</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(L.) Tzvelev</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
@@ -7178,10 +7178,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>609404</v>
+        <v>609400.5996320476</v>
       </c>
       <c r="R59" t="n">
-        <v>7179337</v>
+        <v>7179478.972150498</v>
       </c>
       <c r="S59" t="n">
         <v>25</v>
@@ -7213,7 +7213,7 @@
       </c>
       <c r="Z59" t="inlineStr">
         <is>
-          <t>14:12</t>
+          <t>13:56</t>
         </is>
       </c>
       <c r="AA59" t="inlineStr">
@@ -7223,7 +7223,7 @@
       </c>
       <c r="AB59" t="inlineStr">
         <is>
-          <t>14:12</t>
+          <t>13:56</t>
         </is>
       </c>
       <c r="AD59" t="b">
@@ -7250,10 +7250,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>103249634</v>
+        <v>103249623</v>
       </c>
       <c r="B60" t="n">
-        <v>73686</v>
+        <v>76863</v>
       </c>
       <c r="C60" t="inlineStr">
         <is>
@@ -7262,25 +7262,25 @@
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E60" t="n">
-        <v>308</v>
+        <v>498</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Brunpudrad nållav</t>
+          <t>Liten sotlav</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Chaenotheca gracillima</t>
+          <t>Acolium karelicum</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Vain.) M.Prieto &amp; Wedin</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
@@ -7290,10 +7290,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>609400.5996320476</v>
+        <v>609413.9065085755</v>
       </c>
       <c r="R60" t="n">
-        <v>7179478.972150498</v>
+        <v>7179360.088357097</v>
       </c>
       <c r="S60" t="n">
         <v>25</v>
@@ -7325,7 +7325,7 @@
       </c>
       <c r="Z60" t="inlineStr">
         <is>
-          <t>13:56</t>
+          <t>14:11</t>
         </is>
       </c>
       <c r="AA60" t="inlineStr">
@@ -7335,7 +7335,7 @@
       </c>
       <c r="AB60" t="inlineStr">
         <is>
-          <t>13:56</t>
+          <t>14:11</t>
         </is>
       </c>
       <c r="AD60" t="b">
@@ -7362,10 +7362,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>103249623</v>
+        <v>103250071</v>
       </c>
       <c r="B61" t="n">
-        <v>76863</v>
+        <v>56395</v>
       </c>
       <c r="C61" t="inlineStr">
         <is>
@@ -7374,38 +7374,43 @@
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E61" t="n">
-        <v>498</v>
+        <v>100109</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Liten sotlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Acolium karelicum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Vain.) M.Prieto &amp; Wedin</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
+      <c r="M61" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P61" t="inlineStr">
         <is>
           <t>Baksjöån, Ås lm</t>
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>609413.9065085755</v>
+        <v>609443.9336626019</v>
       </c>
       <c r="R61" t="n">
-        <v>7179360.088357097</v>
+        <v>7179441.611275527</v>
       </c>
       <c r="S61" t="n">
         <v>25</v>
@@ -7437,7 +7442,7 @@
       </c>
       <c r="Z61" t="inlineStr">
         <is>
-          <t>14:11</t>
+          <t>14:04</t>
         </is>
       </c>
       <c r="AA61" t="inlineStr">
@@ -7447,7 +7452,7 @@
       </c>
       <c r="AB61" t="inlineStr">
         <is>
-          <t>14:11</t>
+          <t>14:04</t>
         </is>
       </c>
       <c r="AD61" t="b">
@@ -7474,10 +7479,10 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>103250071</v>
+        <v>103249693</v>
       </c>
       <c r="B62" t="n">
-        <v>56395</v>
+        <v>73698</v>
       </c>
       <c r="C62" t="inlineStr">
         <is>
@@ -7490,39 +7495,34 @@
         </is>
       </c>
       <c r="E62" t="n">
-        <v>100109</v>
+        <v>1467</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Rödbrun blekspik</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Sclerophora coniophaea</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Norman) J.Mattsson &amp; Middelb.</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
-      <c r="M62" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P62" t="inlineStr">
         <is>
           <t>Baksjöån, Ås lm</t>
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>609443.9336626019</v>
+        <v>609320.4498408573</v>
       </c>
       <c r="R62" t="n">
-        <v>7179441.611275527</v>
+        <v>7179090.141812022</v>
       </c>
       <c r="S62" t="n">
         <v>25</v>
@@ -7554,7 +7554,7 @@
       </c>
       <c r="Z62" t="inlineStr">
         <is>
-          <t>14:04</t>
+          <t>11:02</t>
         </is>
       </c>
       <c r="AA62" t="inlineStr">
@@ -7564,7 +7564,7 @@
       </c>
       <c r="AB62" t="inlineStr">
         <is>
-          <t>14:04</t>
+          <t>11:02</t>
         </is>
       </c>
       <c r="AD62" t="b">
@@ -7591,10 +7591,10 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>103249693</v>
+        <v>103249633</v>
       </c>
       <c r="B63" t="n">
-        <v>73698</v>
+        <v>77506</v>
       </c>
       <c r="C63" t="inlineStr">
         <is>
@@ -7607,21 +7607,21 @@
         </is>
       </c>
       <c r="E63" t="n">
-        <v>1467</v>
+        <v>6425</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Rödbrun blekspik</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Sclerophora coniophaea</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Norman) J.Mattsson &amp; Middelb.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
@@ -7631,10 +7631,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>609320.4498408573</v>
+        <v>609401.4242259815</v>
       </c>
       <c r="R63" t="n">
-        <v>7179090.141812022</v>
+        <v>7179479.857708881</v>
       </c>
       <c r="S63" t="n">
         <v>25</v>
@@ -7666,7 +7666,7 @@
       </c>
       <c r="Z63" t="inlineStr">
         <is>
-          <t>11:02</t>
+          <t>13:56</t>
         </is>
       </c>
       <c r="AA63" t="inlineStr">
@@ -7676,7 +7676,7 @@
       </c>
       <c r="AB63" t="inlineStr">
         <is>
-          <t>11:02</t>
+          <t>13:56</t>
         </is>
       </c>
       <c r="AD63" t="b">
@@ -7703,10 +7703,10 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>103249633</v>
+        <v>103250086</v>
       </c>
       <c r="B64" t="n">
-        <v>77506</v>
+        <v>56395</v>
       </c>
       <c r="C64" t="inlineStr">
         <is>
@@ -7719,34 +7719,39 @@
         </is>
       </c>
       <c r="E64" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
+      <c r="M64" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P64" t="inlineStr">
         <is>
           <t>Baksjöån, Ås lm</t>
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>609401.4242259815</v>
+        <v>609242.1918445774</v>
       </c>
       <c r="R64" t="n">
-        <v>7179479.857708881</v>
+        <v>7178967.926208255</v>
       </c>
       <c r="S64" t="n">
         <v>25</v>
@@ -7778,7 +7783,7 @@
       </c>
       <c r="Z64" t="inlineStr">
         <is>
-          <t>13:56</t>
+          <t>10:43</t>
         </is>
       </c>
       <c r="AA64" t="inlineStr">
@@ -7788,7 +7793,7 @@
       </c>
       <c r="AB64" t="inlineStr">
         <is>
-          <t>13:56</t>
+          <t>10:43</t>
         </is>
       </c>
       <c r="AD64" t="b">
@@ -7815,10 +7820,10 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>103250078</v>
+        <v>103249696</v>
       </c>
       <c r="B65" t="n">
-        <v>56395</v>
+        <v>73693</v>
       </c>
       <c r="C65" t="inlineStr">
         <is>
@@ -7831,39 +7836,34 @@
         </is>
       </c>
       <c r="E65" t="n">
-        <v>100109</v>
+        <v>6440</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
-      <c r="M65" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P65" t="inlineStr">
         <is>
           <t>Baksjöån, Ås lm</t>
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>609245.5053856794</v>
+        <v>609287.5033891089</v>
       </c>
       <c r="R65" t="n">
-        <v>7179550.787618494</v>
+        <v>7178994.384986188</v>
       </c>
       <c r="S65" t="n">
         <v>25</v>
@@ -7895,7 +7895,7 @@
       </c>
       <c r="Z65" t="inlineStr">
         <is>
-          <t>13:31</t>
+          <t>10:49</t>
         </is>
       </c>
       <c r="AA65" t="inlineStr">
@@ -7905,7 +7905,7 @@
       </c>
       <c r="AB65" t="inlineStr">
         <is>
-          <t>13:31</t>
+          <t>10:49</t>
         </is>
       </c>
       <c r="AD65" t="b">
@@ -7932,10 +7932,10 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>103250086</v>
+        <v>103249688</v>
       </c>
       <c r="B66" t="n">
-        <v>56395</v>
+        <v>96354</v>
       </c>
       <c r="C66" t="inlineStr">
         <is>
@@ -7944,43 +7944,38 @@
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E66" t="n">
-        <v>100109</v>
+        <v>221952</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
-      <c r="M66" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P66" t="inlineStr">
         <is>
           <t>Baksjöån, Ås lm</t>
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>609242.1918445774</v>
+        <v>609282.19026173</v>
       </c>
       <c r="R66" t="n">
-        <v>7178967.926208255</v>
+        <v>7179117.423807778</v>
       </c>
       <c r="S66" t="n">
         <v>25</v>
@@ -8012,7 +8007,7 @@
       </c>
       <c r="Z66" t="inlineStr">
         <is>
-          <t>10:43</t>
+          <t>11:09</t>
         </is>
       </c>
       <c r="AA66" t="inlineStr">
@@ -8022,7 +8017,7 @@
       </c>
       <c r="AB66" t="inlineStr">
         <is>
-          <t>10:43</t>
+          <t>11:09</t>
         </is>
       </c>
       <c r="AD66" t="b">
@@ -8049,10 +8044,10 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>103249696</v>
+        <v>103250079</v>
       </c>
       <c r="B67" t="n">
-        <v>73693</v>
+        <v>56395</v>
       </c>
       <c r="C67" t="inlineStr">
         <is>
@@ -8065,34 +8060,39 @@
         </is>
       </c>
       <c r="E67" t="n">
-        <v>6440</v>
+        <v>100109</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
+      <c r="M67" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P67" t="inlineStr">
         <is>
           <t>Baksjöån, Ås lm</t>
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>609287.5033891089</v>
+        <v>609195.8830579831</v>
       </c>
       <c r="R67" t="n">
-        <v>7178994.384986188</v>
+        <v>7179513.482143113</v>
       </c>
       <c r="S67" t="n">
         <v>25</v>
@@ -8124,7 +8124,7 @@
       </c>
       <c r="Z67" t="inlineStr">
         <is>
-          <t>10:49</t>
+          <t>13:20</t>
         </is>
       </c>
       <c r="AA67" t="inlineStr">
@@ -8134,7 +8134,7 @@
       </c>
       <c r="AB67" t="inlineStr">
         <is>
-          <t>10:49</t>
+          <t>13:20</t>
         </is>
       </c>
       <c r="AD67" t="b">
@@ -8161,10 +8161,10 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>103249688</v>
+        <v>105963070</v>
       </c>
       <c r="B68" t="n">
-        <v>96354</v>
+        <v>76487</v>
       </c>
       <c r="C68" t="inlineStr">
         <is>
@@ -8173,25 +8173,25 @@
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E68" t="n">
-        <v>221952</v>
+        <v>1794</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Rödskaftad svartspik</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Chaenothecopsis haematopus</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
@@ -8201,10 +8201,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>609282.19026173</v>
+        <v>609112.1549435256</v>
       </c>
       <c r="R68" t="n">
-        <v>7179117.423807778</v>
+        <v>7179258.456105179</v>
       </c>
       <c r="S68" t="n">
         <v>25</v>
@@ -8236,7 +8236,7 @@
       </c>
       <c r="Z68" t="inlineStr">
         <is>
-          <t>11:09</t>
+          <t>11:37</t>
         </is>
       </c>
       <c r="AA68" t="inlineStr">
@@ -8246,7 +8246,7 @@
       </c>
       <c r="AB68" t="inlineStr">
         <is>
-          <t>11:09</t>
+          <t>11:37</t>
         </is>
       </c>
       <c r="AD68" t="b">
@@ -8257,6 +8257,31 @@
       </c>
       <c r="AG68" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ68" t="inlineStr">
+        <is>
+          <t>granticka</t>
+        </is>
+      </c>
+      <c r="AK68" t="inlineStr">
+        <is>
+          <t>Porodaedalea chrysoloma</t>
+        </is>
+      </c>
+      <c r="AO68" t="inlineStr">
+        <is>
+          <t>Porodaedalea chrysoloma</t>
+        </is>
+      </c>
+      <c r="AQ68" t="inlineStr">
+        <is>
+          <t>Isak Vahlström</t>
+        </is>
+      </c>
+      <c r="AR68" t="inlineStr">
+        <is>
+          <t>2208221137</t>
+        </is>
       </c>
       <c r="AT68" t="inlineStr"/>
       <c r="AW68" t="inlineStr">
@@ -8273,10 +8298,10 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>103250079</v>
+        <v>106008761</v>
       </c>
       <c r="B69" t="n">
-        <v>56395</v>
+        <v>76487</v>
       </c>
       <c r="C69" t="inlineStr">
         <is>
@@ -8285,43 +8310,38 @@
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E69" t="n">
-        <v>100109</v>
+        <v>1794</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Rödskaftad svartspik</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Chaenothecopsis haematopus</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
-      <c r="M69" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P69" t="inlineStr">
         <is>
           <t>Baksjöån, Ås lm</t>
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>609195.8830579831</v>
+        <v>609291.3806474744</v>
       </c>
       <c r="R69" t="n">
-        <v>7179513.482143113</v>
+        <v>7179561.433374308</v>
       </c>
       <c r="S69" t="n">
         <v>25</v>
@@ -8353,7 +8373,7 @@
       </c>
       <c r="Z69" t="inlineStr">
         <is>
-          <t>13:20</t>
+          <t>13:44</t>
         </is>
       </c>
       <c r="AA69" t="inlineStr">
@@ -8363,7 +8383,7 @@
       </c>
       <c r="AB69" t="inlineStr">
         <is>
-          <t>13:20</t>
+          <t>13:44</t>
         </is>
       </c>
       <c r="AD69" t="b">
@@ -8374,6 +8394,31 @@
       </c>
       <c r="AG69" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ69" t="inlineStr">
+        <is>
+          <t>granticka</t>
+        </is>
+      </c>
+      <c r="AK69" t="inlineStr">
+        <is>
+          <t>Porodaedalea chrysoloma</t>
+        </is>
+      </c>
+      <c r="AO69" t="inlineStr">
+        <is>
+          <t>Porodaedalea chrysoloma</t>
+        </is>
+      </c>
+      <c r="AQ69" t="inlineStr">
+        <is>
+          <t>Isak Vahlström</t>
+        </is>
+      </c>
+      <c r="AR69" t="inlineStr">
+        <is>
+          <t>2208221344</t>
+        </is>
       </c>
       <c r="AT69" t="inlineStr"/>
       <c r="AW69" t="inlineStr">
@@ -8387,280 +8432,6 @@
         </is>
       </c>
       <c r="AY69" t="inlineStr"/>
-    </row>
-    <row r="70">
-      <c r="A70" t="n">
-        <v>105963070</v>
-      </c>
-      <c r="B70" t="n">
-        <v>76487</v>
-      </c>
-      <c r="C70" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
-      </c>
-      <c r="D70" t="inlineStr">
-        <is>
-          <t>VU</t>
-        </is>
-      </c>
-      <c r="E70" t="n">
-        <v>1794</v>
-      </c>
-      <c r="F70" t="inlineStr">
-        <is>
-          <t>Rödskaftad svartspik</t>
-        </is>
-      </c>
-      <c r="G70" t="inlineStr">
-        <is>
-          <t>Chaenothecopsis haematopus</t>
-        </is>
-      </c>
-      <c r="H70" t="inlineStr">
-        <is>
-          <t>Tibell</t>
-        </is>
-      </c>
-      <c r="I70" t="inlineStr"/>
-      <c r="P70" t="inlineStr">
-        <is>
-          <t>Baksjöån, Ås lm</t>
-        </is>
-      </c>
-      <c r="Q70" t="n">
-        <v>609112.1549435256</v>
-      </c>
-      <c r="R70" t="n">
-        <v>7179258.456105179</v>
-      </c>
-      <c r="S70" t="n">
-        <v>25</v>
-      </c>
-      <c r="T70" t="inlineStr">
-        <is>
-          <t>Västerbotten</t>
-        </is>
-      </c>
-      <c r="U70" t="inlineStr">
-        <is>
-          <t>Vilhelmina</t>
-        </is>
-      </c>
-      <c r="V70" t="inlineStr">
-        <is>
-          <t>Åsele lappmark</t>
-        </is>
-      </c>
-      <c r="W70" t="inlineStr">
-        <is>
-          <t>Vilhelmina</t>
-        </is>
-      </c>
-      <c r="Y70" t="inlineStr">
-        <is>
-          <t>2022-08-22</t>
-        </is>
-      </c>
-      <c r="Z70" t="inlineStr">
-        <is>
-          <t>11:37</t>
-        </is>
-      </c>
-      <c r="AA70" t="inlineStr">
-        <is>
-          <t>2022-08-22</t>
-        </is>
-      </c>
-      <c r="AB70" t="inlineStr">
-        <is>
-          <t>11:37</t>
-        </is>
-      </c>
-      <c r="AD70" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE70" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG70" t="b">
-        <v>0</v>
-      </c>
-      <c r="AJ70" t="inlineStr">
-        <is>
-          <t>granticka</t>
-        </is>
-      </c>
-      <c r="AK70" t="inlineStr">
-        <is>
-          <t>Porodaedalea chrysoloma</t>
-        </is>
-      </c>
-      <c r="AO70" t="inlineStr">
-        <is>
-          <t>Porodaedalea chrysoloma</t>
-        </is>
-      </c>
-      <c r="AQ70" t="inlineStr">
-        <is>
-          <t>Isak Vahlström</t>
-        </is>
-      </c>
-      <c r="AR70" t="inlineStr">
-        <is>
-          <t>2208221137</t>
-        </is>
-      </c>
-      <c r="AT70" t="inlineStr"/>
-      <c r="AW70" t="inlineStr">
-        <is>
-          <t>Isak Vahlström</t>
-        </is>
-      </c>
-      <c r="AX70" t="inlineStr">
-        <is>
-          <t>Isak Vahlström</t>
-        </is>
-      </c>
-      <c r="AY70" t="inlineStr"/>
-    </row>
-    <row r="71">
-      <c r="A71" t="n">
-        <v>106008761</v>
-      </c>
-      <c r="B71" t="n">
-        <v>76487</v>
-      </c>
-      <c r="C71" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
-      </c>
-      <c r="D71" t="inlineStr">
-        <is>
-          <t>VU</t>
-        </is>
-      </c>
-      <c r="E71" t="n">
-        <v>1794</v>
-      </c>
-      <c r="F71" t="inlineStr">
-        <is>
-          <t>Rödskaftad svartspik</t>
-        </is>
-      </c>
-      <c r="G71" t="inlineStr">
-        <is>
-          <t>Chaenothecopsis haematopus</t>
-        </is>
-      </c>
-      <c r="H71" t="inlineStr">
-        <is>
-          <t>Tibell</t>
-        </is>
-      </c>
-      <c r="I71" t="inlineStr"/>
-      <c r="P71" t="inlineStr">
-        <is>
-          <t>Baksjöån, Ås lm</t>
-        </is>
-      </c>
-      <c r="Q71" t="n">
-        <v>609291.3806474744</v>
-      </c>
-      <c r="R71" t="n">
-        <v>7179561.433374308</v>
-      </c>
-      <c r="S71" t="n">
-        <v>25</v>
-      </c>
-      <c r="T71" t="inlineStr">
-        <is>
-          <t>Västerbotten</t>
-        </is>
-      </c>
-      <c r="U71" t="inlineStr">
-        <is>
-          <t>Vilhelmina</t>
-        </is>
-      </c>
-      <c r="V71" t="inlineStr">
-        <is>
-          <t>Åsele lappmark</t>
-        </is>
-      </c>
-      <c r="W71" t="inlineStr">
-        <is>
-          <t>Vilhelmina</t>
-        </is>
-      </c>
-      <c r="Y71" t="inlineStr">
-        <is>
-          <t>2022-08-22</t>
-        </is>
-      </c>
-      <c r="Z71" t="inlineStr">
-        <is>
-          <t>13:44</t>
-        </is>
-      </c>
-      <c r="AA71" t="inlineStr">
-        <is>
-          <t>2022-08-22</t>
-        </is>
-      </c>
-      <c r="AB71" t="inlineStr">
-        <is>
-          <t>13:44</t>
-        </is>
-      </c>
-      <c r="AD71" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE71" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG71" t="b">
-        <v>0</v>
-      </c>
-      <c r="AJ71" t="inlineStr">
-        <is>
-          <t>granticka</t>
-        </is>
-      </c>
-      <c r="AK71" t="inlineStr">
-        <is>
-          <t>Porodaedalea chrysoloma</t>
-        </is>
-      </c>
-      <c r="AO71" t="inlineStr">
-        <is>
-          <t>Porodaedalea chrysoloma</t>
-        </is>
-      </c>
-      <c r="AQ71" t="inlineStr">
-        <is>
-          <t>Isak Vahlström</t>
-        </is>
-      </c>
-      <c r="AR71" t="inlineStr">
-        <is>
-          <t>2208221344</t>
-        </is>
-      </c>
-      <c r="AT71" t="inlineStr"/>
-      <c r="AW71" t="inlineStr">
-        <is>
-          <t>Isak Vahlström</t>
-        </is>
-      </c>
-      <c r="AX71" t="inlineStr">
-        <is>
-          <t>Isak Vahlström</t>
-        </is>
-      </c>
-      <c r="AY71" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
